--- a/artfynd/A 22119-2024 artfynd.xlsx
+++ b/artfynd/A 22119-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124661233</v>
+        <v>124661232</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609042</v>
+        <v>608977</v>
       </c>
       <c r="R2" t="n">
-        <v>7029354</v>
+        <v>7029331</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124661232</v>
+        <v>124661233</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>608977</v>
+        <v>609042</v>
       </c>
       <c r="R3" t="n">
-        <v>7029331</v>
+        <v>7029354</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>

--- a/artfynd/A 22119-2024 artfynd.xlsx
+++ b/artfynd/A 22119-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124661232</v>
+        <v>124661233</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>608977</v>
+        <v>609042</v>
       </c>
       <c r="R2" t="n">
-        <v>7029331</v>
+        <v>7029354</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124661233</v>
+        <v>124661232</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609042</v>
+        <v>608977</v>
       </c>
       <c r="R3" t="n">
-        <v>7029354</v>
+        <v>7029331</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>

--- a/artfynd/A 22119-2024 artfynd.xlsx
+++ b/artfynd/A 22119-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124661232</v>
+        <v>124661233</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>608977</v>
+        <v>609042</v>
       </c>
       <c r="R2" t="n">
-        <v>7029331</v>
+        <v>7029354</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124661233</v>
+        <v>124661232</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609042</v>
+        <v>608977</v>
       </c>
       <c r="R3" t="n">
-        <v>7029354</v>
+        <v>7029331</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
